--- a/ModdingKit/package/LangMod/EN/ModViewerLang.xlsx
+++ b/ModdingKit/package/LangMod/EN/ModViewerLang.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="193">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -476,6 +476,132 @@
   </si>
   <si>
     <t xml:space="preserve"> または </t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新しいグループ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループに移動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move to group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループから外す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove from group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループを選択</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select a group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループの名前を入力してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter a name for this group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_default_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_rename</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名前を変更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rename</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_disband</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループを解除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ungroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_expand_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すべて展開</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expand all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_collapse_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すべて折りたたむ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collapse all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループを選択してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select a group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_id_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDをコピー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_id_copied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDをクリップボードにコピーしました：#1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID copied to the clipboard: #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_group_color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色を変更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グループを作成</t>
   </si>
 </sst>
 </file>
@@ -847,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1232,189 +1358,321 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>175</v>
+      </c>
+      <c r="C60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
